--- a/forms/trg/Formulir_TRG_cocoa-rg.xlsx
+++ b/forms/trg/Formulir_TRG_cocoa-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Sylvia Sjam</t>
+          <t>Ade Rosmana</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Entomology, Post Harvest Pests, natural plant product, cocoa</t>
+          <t>Phytopathology, mycology, biological control, environmental management, cocoa</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +933,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>25638652500</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Nasaruddin</t>
+          <t>Sylvia Sjam</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Plant Physiology, Agronomy, Perennial crops</t>
+          <t>Entomology, Post Harvest Pests, natural plant product, cocoa</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Junaid</t>
+          <t>Nasaruddin</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology, plant-microbe interactions, IoT for plant protection</t>
+          <t>Plant Physiology, Agronomy, Perennial crops</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Arsyad</t>
+          <t>Muhammad Junaid</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Economics and Rural Development</t>
+          <t>Phytopathology, plant-microbe interactions, IoT for plant protection</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Salengke</t>
+          <t>Muhammad Arsyad</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Food Process Engineering</t>
+          <t>Agricultural Economics and Rural Development</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Asti Irawanti Azis</t>
+          <t>Salengke</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology</t>
+          <t>Food Process Engineering</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Asman</t>
+          <t>Asti Irawanti Azis</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology, Plant disease epidemiology, biological control, cocoa diseases</t>
+          <t>Phytopathology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Vien Sartika Dewi</t>
+          <t>Asman</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Entomology, biodiversity</t>
+          <t>Phytopathology, Plant disease epidemiology, biological control, cocoa diseases</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Andi Amrullah</t>
+          <t>Vien Sartika Dewi</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Socio Economic of agriculture</t>
+          <t>Entomology, biodiversity</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ruben Sakrabani</t>
+          <t>Andi Amrullah</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Cranfield University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Entomology</t>
+          <t>Socio Economic of agriculture</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Nur Azizah Fitriyanti</t>
+          <t>Ruben Sakrabani</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Cranfield University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Agung Wardiman</t>
+          <t>Nur Azizah Fitriyanti</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1357,22 +1357,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Agraputra Rivay</t>
+          <t>Muhammad Agung Wardiman</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Cocoa R&amp;D</t>
+          <t>Entomology</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1394,22 +1394,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>I M Sahcaesar Syahruddin</t>
+          <t>Muhammad Agraputra Rivay</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Cocoa R&amp;D</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1429,10 +1429,26 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>I M Sahcaesar Syahruddin</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1440,7 +1456,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1629,15 +1649,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
